--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T10:02:39+00:00</t>
+    <t>2024-03-19T08:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:36:19+00:00</t>
+    <t>2024-04-03T13:59:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T13:59:51+00:00</t>
+    <t>2024-04-03T14:08:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:18:25+00:00</t>
+    <t>2024-04-03T14:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:35:17+00:00</t>
+    <t>2024-04-03T14:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-3</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T14:54:13+00:00</t>
+    <t>2024-04-08T13:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr, monserviceclient.annuaire@esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:06:58+00:00</t>
+    <t>2024-04-08T13:14:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:14:28+00:00</t>
+    <t>2024-04-08T13:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T13:35:38+00:00</t>
+    <t>2024-04-08T14:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -389,8 +389,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t>ele-1
-per-1</t>
+    <t xml:space="preserve">per-1
+</t>
   </si>
   <si>
     <t>./low</t>
@@ -1193,7 +1193,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1401,7 +1401,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>106</v>
@@ -1609,13 +1609,13 @@
         <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" hidden="true">

--- a/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/nr-add-mapping/ig/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T14:07:36+00:00</t>
+    <t>2024-04-08T14:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
